--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260915.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260915.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>137,405</t>
+          <t>137,855</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.36%</t>
+          <t>26.19%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>99,560</t>
+          <t>99,890</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>7.85%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,585</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.59%</t>
+          <t>7.75%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,645</t>
+          <t>50,815</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>6.31%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>120,725</t>
+          <t>121,125</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.50%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,410</t>
+          <t>59,610</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.74%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>18,183</t>
+          <t>18,283</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>65,145</t>
+          <t>5,735</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,635</t>
+          <t>65,355</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>45,095</t>
+          <t>45,245</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,625</t>
+          <t>19,725</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>76,695</t>
+          <t>76,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>31,330</t>
+          <t>31,430</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>20,145</t>
+          <t>20,245</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>50,725</t>
+          <t>50,895</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,176 +931,176 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,478</t>
+          <t>19,490</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>19,390</t>
+          <t>26,578</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>35,950</t>
+          <t>85,144,112</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>59,098</t>
+          <t>36,050</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>59,298</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,890</t>
+          <t>21,408</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>63,644,112</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18,355</t>
+          <t>18,455</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>125,785</t>
+          <t>126,205</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1188,46 +1188,46 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>42,830</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,240</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>9,536</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>407,876</t>
+          <t>980,194</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>572,318</t>
+          <t>-235,486</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
